--- a/excel_files/11.7.1.a.xlsx
+++ b/excel_files/11.7.1.a.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korozbaeva\Desktop\Показатели ЦУР для Платформы\Национальные показатели ЦУР\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Показатели ЦУР для Платформы\Национальные показатели ЦУР — 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEF7E067-C755-4449-96BA-E8C505A9B1FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -24,12 +25,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -157,7 +152,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -294,7 +289,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -350,12 +345,25 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Normal 17" xfId="1"/>
-    <cellStyle name="Normal 2" xfId="3"/>
+    <cellStyle name="Normal 17" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Normal 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 7" xfId="2"/>
+    <cellStyle name="Обычный 7" xfId="2" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -632,8 +640,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:M14"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="37.7109375" style="7" customWidth="1"/>
@@ -641,7 +649,7 @@
     <col min="9" max="16384" width="9.140625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>15</v>
       </c>
@@ -655,7 +663,7 @@
       <c r="E1" s="10"/>
       <c r="F1" s="10"/>
     </row>
-    <row r="2" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>17</v>
       </c>
@@ -666,8 +674,10 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M3" s="19"/>
+    </row>
+    <row r="4" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
@@ -704,8 +714,11 @@
       <c r="L4" s="1">
         <v>2023</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M4" s="20">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>19</v>
       </c>
@@ -742,8 +755,11 @@
       <c r="L5" s="16">
         <v>1.6430457248453274</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M5" s="22">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>20</v>
       </c>
@@ -780,8 +796,11 @@
       <c r="L6" s="17">
         <v>0.41181606829870221</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M6" s="21">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>21</v>
       </c>
@@ -818,8 +837,11 @@
       <c r="L7" s="17">
         <v>0.94796963217320562</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M7" s="21">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>22</v>
       </c>
@@ -856,8 +878,11 @@
       <c r="L8" s="17">
         <v>0.72306112208737106</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M8" s="21">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>23</v>
       </c>
@@ -894,8 +919,11 @@
       <c r="L9" s="17">
         <v>2.1802539701246277</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M9" s="21">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>28</v>
       </c>
@@ -932,8 +960,11 @@
       <c r="L10" s="17">
         <v>0.63651150401750112</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M10" s="21">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>24</v>
       </c>
@@ -970,8 +1001,11 @@
       <c r="L11" s="17">
         <v>0.97994201681774651</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M11" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>25</v>
       </c>
@@ -1008,8 +1042,11 @@
       <c r="L12" s="17">
         <v>2.2469385026996971</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M12" s="21">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>26</v>
       </c>
@@ -1046,8 +1083,11 @@
       <c r="L13" s="17">
         <v>4.1686356866605365</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M13" s="21">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
         <v>27</v>
       </c>
@@ -1083,6 +1123,9 @@
       </c>
       <c r="L14" s="18">
         <v>0.3304193846038968</v>
+      </c>
+      <c r="M14" s="23">
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>
